--- a/ig/nr-add-details-about-patient-ins/CodeSystem-fr-core-location-type.xlsx
+++ b/ig/nr-add-details-about-patient-ins/CodeSystem-fr-core-location-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T16:56:43+00:00</t>
+    <t>2024-01-08T13:38:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
